--- a/data/sars/pacific/tables/Pacific_2009_Appendix3.xlsx
+++ b/data/sars/pacific/tables/Pacific_2009_Appendix3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/pacific/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FF3E057-0B7C-C74A-879B-9A5DDB8937E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B580B4BD-50D5-8B4B-AEB6-58D9E7908EEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="500" windowWidth="32700" windowHeight="20180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="104">
   <si>
     <t>California sea lion</t>
   </si>
@@ -313,9 +313,6 @@
     <t>Eastern North Pacific Southern Resident</t>
   </si>
   <si>
-    <t>revised</t>
-  </si>
-  <si>
     <t>≥3.6</t>
   </si>
   <si>
@@ -326,6 +323,15 @@
   </si>
   <si>
     <t>rf</t>
+  </si>
+  <si>
+    <t>revised_yn</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>revision_yr</t>
   </si>
 </sst>
 </file>
@@ -771,8 +777,7 @@
     <col min="11" max="11" width="15.3984375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.3984375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="15" width="9.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="21.59765625" style="1" customWidth="1"/>
+    <col min="16" max="17" width="13.3984375" style="1" customWidth="1"/>
     <col min="18" max="21" width="9.796875" style="1" customWidth="1"/>
     <col min="22" max="16384" width="9" style="1"/>
   </cols>
@@ -800,7 +805,7 @@
         <v>87</v>
       </c>
       <c r="H1" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I1" s="15" t="s">
         <v>88</v>
@@ -824,9 +829,11 @@
         <v>94</v>
       </c>
       <c r="P1" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q1" s="15"/>
+        <v>103</v>
+      </c>
+      <c r="Q1" s="15" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="2" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
@@ -1215,6 +1222,9 @@
       <c r="P9" s="14">
         <v>2009</v>
       </c>
+      <c r="Q9" s="1" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="10" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A10" s="4" t="s">
@@ -1265,6 +1275,9 @@
       <c r="P10" s="14">
         <v>2009</v>
       </c>
+      <c r="Q10" s="1" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="11" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
@@ -1315,6 +1328,9 @@
       <c r="P11" s="14">
         <v>2009</v>
       </c>
+      <c r="Q11" s="1" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="12" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A12" s="4" t="s">
@@ -1365,6 +1381,9 @@
       <c r="P12" s="14">
         <v>2009</v>
       </c>
+      <c r="Q12" s="1" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="13" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A13" s="4" t="s">
@@ -1415,6 +1434,9 @@
       <c r="P13" s="14">
         <v>2009</v>
       </c>
+      <c r="Q13" s="1" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="14" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A14" s="4" t="s">
@@ -1465,6 +1487,9 @@
       <c r="P14" s="14">
         <v>2009</v>
       </c>
+      <c r="Q14" s="1" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="15" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
@@ -1566,7 +1591,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
         <v>41</v>
       </c>
@@ -1616,7 +1641,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
         <v>42</v>
       </c>
@@ -1666,7 +1691,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
         <v>43</v>
       </c>
@@ -1716,7 +1741,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
         <v>43</v>
       </c>
@@ -1766,7 +1791,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
         <v>46</v>
       </c>
@@ -1816,7 +1841,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
         <v>47</v>
       </c>
@@ -1866,7 +1891,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
         <v>48</v>
       </c>
@@ -1916,7 +1941,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
         <v>49</v>
       </c>
@@ -1966,7 +1991,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A25" s="2" t="s">
         <v>50</v>
       </c>
@@ -2016,7 +2041,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A26" s="4" t="s">
         <v>50</v>
       </c>
@@ -2065,8 +2090,11 @@
       <c r="P26" s="14">
         <v>2008</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q26" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
         <v>52</v>
       </c>
@@ -2116,7 +2144,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
         <v>53</v>
       </c>
@@ -2166,7 +2194,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
         <v>54</v>
       </c>
@@ -2216,7 +2244,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
         <v>55</v>
       </c>
@@ -2266,7 +2294,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
         <v>56</v>
       </c>
@@ -2295,10 +2323,10 @@
         <v>30</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>6</v>
@@ -2316,7 +2344,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
         <v>57</v>
       </c>
@@ -2445,10 +2473,10 @@
         <v>2.5</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L34" s="4" t="s">
         <v>23</v>
@@ -2464,6 +2492,9 @@
       </c>
       <c r="P34" s="14">
         <v>2009</v>
+      </c>
+      <c r="Q34" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="15" x14ac:dyDescent="0.15">
@@ -2515,6 +2546,9 @@
       <c r="P35" s="14">
         <v>2009</v>
       </c>
+      <c r="Q35" s="1" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="36" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="s">
@@ -3163,7 +3197,9 @@
       <c r="P48" s="14">
         <v>2009</v>
       </c>
-      <c r="Q48" s="3"/>
+      <c r="Q48" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="R48" s="3"/>
     </row>
     <row r="49" spans="1:18" ht="15" x14ac:dyDescent="0.15">
@@ -3211,7 +3247,9 @@
       <c r="P49" s="14">
         <v>2009</v>
       </c>
-      <c r="Q49" s="3"/>
+      <c r="Q49" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="R49" s="3"/>
     </row>
     <row r="50" spans="1:18" ht="15" x14ac:dyDescent="0.15">
@@ -3263,7 +3301,9 @@
       <c r="P50" s="14">
         <v>2009</v>
       </c>
-      <c r="Q50" s="3"/>
+      <c r="Q50" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="R50" s="3"/>
     </row>
     <row r="51" spans="1:18" ht="15" x14ac:dyDescent="0.15">
@@ -3917,7 +3957,7 @@
         <v>59</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>2</v>
@@ -3958,7 +3998,9 @@
       <c r="P64" s="4">
         <v>2009</v>
       </c>
-      <c r="Q64" s="3"/>
+      <c r="Q64" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="R64" s="3"/>
     </row>
   </sheetData>
